--- a/data/trans_orig/IP07KS_C05_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP07KS_C05_2023-Edad-trans_orig.xlsx
@@ -535,13 +535,13 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según la frecuencia de tener suficiente tiempo para sí mismo/a en 2023 (tasa de respuesta: 99,83%)</t>
+          <t>Menores según la frecuencia de tener suficiente tiempo para sí mismo/a, percibida por el/la menor en 2023 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>40397</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>31585</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>49285</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>41,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>32,06%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>50,03%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>28409</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>22090</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>35709</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>41,82%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>32,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>52,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>41887</t>
+          <t>29434</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>33551</t>
+          <t>22269</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>51171</t>
+          <t>36718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>41,11%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>31,1%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>70296</t>
+          <t>69831</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59776</t>
+          <t>58445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>82910</t>
+          <t>81227</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>42,02%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>34,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>47,75%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>40256</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>30982</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>49835</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>40,86%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31,45%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>50,58%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>27735</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21206</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>34542</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>40,83%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31,22%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>50,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39632</t>
+          <t>29838</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>30761</t>
+          <t>23397</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>47981</t>
+          <t>37792</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>39,89%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>30,96%</t>
+          <t>32,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>67367</t>
+          <t>70094</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>56529</t>
+          <t>58016</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>77606</t>
+          <t>81706</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>48,03%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9902</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5465</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>16706</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>10,05%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>16,96%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>7391</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3648</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>12304</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>10,88%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>5,37%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,11%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9876</t>
+          <t>7838</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5260</t>
+          <t>3730</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>16736</t>
+          <t>13696</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>19,13%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>17267</t>
+          <t>17740</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>11900</t>
+          <t>11108</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26298</t>
+          <t>25934</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>15,24%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2685</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>501</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8459</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,73%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,51%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>8,59%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>4390</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1629</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>9453</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>6,46%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>13,92%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2863</t>
+          <t>4496</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>1777</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>10020</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>7253</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>3349</t>
+          <t>3184</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14360</t>
+          <t>14126</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,3%</t>
         </is>
       </c>
     </row>
@@ -1172,107 +1172,107 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>5278</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2113</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>11483</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>5,36%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2,14%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>11,66%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>5107</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2143</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>10363</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,14%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>10,43%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>5107</t>
+          <t>5278</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1992</t>
+          <t>2109</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11570</t>
+          <t>12285</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,22%</t>
         </is>
       </c>
     </row>
@@ -1285,74 +1285,74 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>98519</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>67925</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>71606</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>99365</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>214</t>
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>167290</t>
+          <t>170125</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>77469</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>63027</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>95365</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>45,15%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>36,73%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>55,58%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>57</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>36259</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>18890</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>48674</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>25,57%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>13,32%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>34,33%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>79671</t>
+          <t>37884</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>65381</t>
+          <t>30385</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>100126</t>
+          <t>48307</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>37,84%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>115929</t>
+          <t>115353</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>86621</t>
+          <t>97145</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>141050</t>
+          <t>136454</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>38,87%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>32,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,98%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>69316</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>54590</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>84074</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>40,4%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>31,82%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>49,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>84</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>82671</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>65268</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>109818</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>58,31%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>46,03%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>77,46%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>81</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>68433</t>
+          <t>61922</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52260</t>
+          <t>50867</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>84010</t>
+          <t>71430</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>49,46%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>40,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>57,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>151105</t>
+          <t>131239</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>126211</t>
+          <t>114510</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>196601</t>
+          <t>149642</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>48,04%</t>
+          <t>44,22%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>38,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>50,42%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>12501</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6847</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>20735</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>7,29%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>3,99%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>12,08%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>27</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>18852</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>9401</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>27740</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>13,3%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>19,57%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11899</t>
+          <t>21168</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6681</t>
+          <t>14624</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20572</t>
+          <t>30421</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>30751</t>
+          <t>33669</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>20628</t>
+          <t>24475</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>42141</t>
+          <t>46407</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>15,64%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>6348</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>12292</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,7%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,76%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>7,16%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>2763</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>614</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>6932</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>1,95%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>4,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6053</t>
+          <t>2875</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2820</t>
+          <t>617</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11596</t>
+          <t>6766</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>8816</t>
+          <t>9223</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4907</t>
+          <t>4973</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>15418</t>
+          <t>15445</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,56%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>5946</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2042</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12769</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,47%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>1,19%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7,44%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>4338</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>0,87%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>4217</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>3,06%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>6727</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>2852</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>15428</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>3,89%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>1,65%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>7963</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>3372</t>
+          <t>3113</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>15618</t>
+          <t>13239</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -1967,74 +1967,74 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>171581</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>141780</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>141780</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>141780</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>125192</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>125192</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>125192</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
+      <c r="P15" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>172783</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
           <t>362</t>
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>314563</t>
+          <t>296773</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>314563</t>
+          <t>296773</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>314563</t>
+          <t>296773</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>117866</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>101462</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>137781</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>43,64%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>37,56%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>51,01%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>64668</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>40955</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>79839</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>30,84%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>19,53%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>38,07%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>121557</t>
+          <t>67318</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>103624</t>
+          <t>57162</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>143032</t>
+          <t>79072</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,08%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>186225</t>
+          <t>185184</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>155270</t>
+          <t>164115</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>214870</t>
+          <t>209276</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>39,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>32,22%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,82%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>109573</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>93460</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>125611</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>40,57%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>34,6%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>46,51%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>123</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>110406</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>91211</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>144134</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>52,65%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>43,49%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>68,73%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>108065</t>
+          <t>91760</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>89311</t>
+          <t>79339</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>126741</t>
+          <t>103427</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>39,71%</t>
+          <t>46,63%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>40,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>218472</t>
+          <t>201333</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>192521</t>
+          <t>180426</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>261467</t>
+          <t>220995</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>45,34%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>39,95%</t>
+          <t>38,64%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,26%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>22403</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>14945</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>33440</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>8,29%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,38%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>26242</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>17308</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>36855</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>12,51%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>8,25%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>17,57%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>21775</t>
+          <t>29005</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>13753</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>31940</t>
+          <t>40186</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>14,74%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,74%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>48017</t>
+          <t>51409</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>36230</t>
+          <t>39370</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>61922</t>
+          <t>66094</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>9,97%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,85%</t>
+          <t>14,16%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>9034</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>4717</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>17382</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>6,44%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>7154</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>3294</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>13524</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>1,57%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>6,45%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8916</t>
+          <t>7371</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>3617</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16042</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>16069</t>
+          <t>16404</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>9467</t>
+          <t>9786</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>24615</t>
+          <t>24949</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,34%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>11225</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>6064</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>19476</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>4,16%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2,24%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>7,21%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>1236</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>1344</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>4400</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>0,59%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>4650</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>2,1%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>11834</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>6551</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>20713</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>4,35%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>2,41%</t>
-        </is>
-      </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>13070</t>
+          <t>12568</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>7634</t>
+          <t>7582</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>22563</t>
+          <t>20241</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,34%</t>
         </is>
       </c>
     </row>
@@ -2649,74 +2649,74 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>270100</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>209705</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>209705</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>209705</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>196798</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>196798</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>196798</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>307</t>
-        </is>
-      </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>272147</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>576</t>
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>481853</t>
+          <t>466898</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
